--- a/development/one_file_rosetta_output/SP112947_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP112947_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -538,7 +550,10 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -566,7 +581,10 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -594,7 +612,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -665,7 +686,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -693,7 +717,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -801,7 +828,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -829,7 +859,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -855,9 +888,12 @@
         </is>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -920,7 +956,10 @@
       <c r="D12" s="4">
         <v>2</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -983,7 +1022,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1046,7 +1088,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1072,9 +1117,12 @@
         </is>
       </c>
       <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1128,9 +1176,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1186,7 +1237,10 @@
       <c r="D17" s="4">
         <v>3</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1242,7 +1296,10 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1270,7 +1327,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1298,7 +1358,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1359,9 +1422,12 @@
         </is>
       </c>
       <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1422,9 +1488,12 @@
         </is>
       </c>
       <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1493,9 +1562,12 @@
         </is>
       </c>
       <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1566,7 +1638,10 @@
       <c r="D24" s="4">
         <v>2</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4">
+        <v>2</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1635,9 +1710,12 @@
         </is>
       </c>
       <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1665,7 +1743,10 @@
       <c r="D26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1751,7 +1832,10 @@
       <c r="D27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1779,7 +1863,10 @@
       <c r="D28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1833,9 +1920,12 @@
         </is>
       </c>
       <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1898,7 +1988,10 @@
       <c r="D30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="4">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1961,7 +2054,10 @@
       <c r="D31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="4">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1987,9 +2083,12 @@
         </is>
       </c>
       <c r="D32" s="4">
-        <v>1</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2015,9 +2114,12 @@
         </is>
       </c>
       <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2086,9 +2188,12 @@
         </is>
       </c>
       <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2159,7 +2264,10 @@
       <c r="D35" s="4">
         <v>2</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4">
+        <v>2</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2228,9 +2336,12 @@
         </is>
       </c>
       <c r="D36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2256,9 +2367,12 @@
         </is>
       </c>
       <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2284,9 +2398,12 @@
         </is>
       </c>
       <c r="D38" s="4">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2372,7 +2489,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2458,7 +2578,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2551,7 +2674,10 @@
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2577,9 +2703,12 @@
         </is>
       </c>
       <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2635,7 +2764,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2689,9 +2821,12 @@
         </is>
       </c>
       <c r="D44" s="4">
-        <v>1</v>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2745,9 +2880,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4">
         <v>2</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2801,9 +2939,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
         <v>3</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2859,7 +3000,10 @@
       <c r="D47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="4">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2920,9 +3064,12 @@
         </is>
       </c>
       <c r="D48" s="4">
-        <v>1</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2983,9 +3130,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>3</v>
+      </c>
+      <c r="E49" s="4">
         <v>2</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3048,7 +3198,10 @@
       <c r="D50" s="4">
         <v>3</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>3</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3109,9 +3262,12 @@
         </is>
       </c>
       <c r="D51" s="4">
-        <v>1</v>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3172,9 +3328,12 @@
         </is>
       </c>
       <c r="D52" s="4">
-        <v>1</v>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3250,9 +3409,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3330,7 +3492,10 @@
       <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3358,7 +3523,10 @@
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3414,7 +3582,10 @@
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3442,7 +3613,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3505,7 +3679,10 @@
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3566,9 +3743,12 @@
         </is>
       </c>
       <c r="D59" s="4">
-        <v>1</v>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3639,7 +3819,10 @@
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3708,9 +3891,12 @@
         </is>
       </c>
       <c r="D61" s="4">
-        <v>1</v>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3738,7 +3924,10 @@
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3824,7 +4013,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3852,7 +4044,10 @@
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3953,7 +4148,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4061,7 +4259,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4089,7 +4290,10 @@
       <c r="D67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4167,7 +4371,10 @@
       <c r="D68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4230,7 +4437,10 @@
       <c r="D69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4258,7 +4468,10 @@
       <c r="D70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4284,9 +4497,12 @@
         </is>
       </c>
       <c r="D71" s="4">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4349,7 +4565,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4410,9 +4629,12 @@
         </is>
       </c>
       <c r="D73" s="4">
-        <v>1</v>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4481,9 +4703,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>3</v>
+      </c>
+      <c r="E74" s="4">
         <v>2</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4552,9 +4777,12 @@
         </is>
       </c>
       <c r="D75" s="4">
-        <v>1</v>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4625,7 +4853,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4653,7 +4884,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4737,9 +4971,12 @@
         </is>
       </c>
       <c r="D78" s="4">
-        <v>1</v>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4830,9 +5067,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>3</v>
+      </c>
+      <c r="E79" s="4">
         <v>2</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4923,9 +5163,12 @@
         </is>
       </c>
       <c r="D80" s="4">
-        <v>1</v>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5016,9 +5259,12 @@
         </is>
       </c>
       <c r="D81" s="4">
-        <v>1</v>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5117,9 +5363,12 @@
         </is>
       </c>
       <c r="D82" s="4">
-        <v>1</v>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5145,9 +5394,12 @@
         </is>
       </c>
       <c r="D83" s="4">
-        <v>1</v>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5248,7 +5500,10 @@
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5354,9 +5609,12 @@
         </is>
       </c>
       <c r="D85" s="4">
-        <v>1</v>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5462,9 +5720,12 @@
         </is>
       </c>
       <c r="D86" s="4">
-        <v>1</v>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5587,7 +5848,10 @@
       <c r="D87" s="4">
         <v>2</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="4">
+        <v>2</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5710,7 +5974,10 @@
       <c r="D88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5736,9 +6003,12 @@
         </is>
       </c>
       <c r="D89" s="4">
-        <v>1</v>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5816,7 +6086,10 @@
       <c r="D90" s="4">
         <v>2</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>2</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5894,7 +6167,10 @@
       <c r="D91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5985,9 +6261,12 @@
         </is>
       </c>
       <c r="D92" s="4">
-        <v>1</v>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E92" s="4">
+        <v>1</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6088,7 +6367,10 @@
       <c r="D93" s="4">
         <v>2</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="4">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6189,7 +6471,10 @@
       <c r="D94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6217,7 +6502,10 @@
       <c r="D95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>1</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6325,7 +6613,10 @@
       <c r="D96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6433,7 +6724,10 @@
       <c r="D97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6461,7 +6755,10 @@
       <c r="D98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="4">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6489,7 +6786,10 @@
       <c r="D99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6515,9 +6815,12 @@
         </is>
       </c>
       <c r="D100" s="4">
-        <v>1</v>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E100" s="4">
+        <v>1</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6640,7 +6943,10 @@
       <c r="D101" s="4">
         <v>2</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4">
+        <v>2</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6761,9 +7067,12 @@
         </is>
       </c>
       <c r="D102" s="4">
-        <v>1</v>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E102" s="4">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6824,9 +7133,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>3</v>
+      </c>
+      <c r="E103" s="4">
         <v>2</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6889,7 +7201,10 @@
       <c r="D104" s="4">
         <v>3</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>3</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6952,7 +7267,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7015,7 +7333,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7043,7 +7364,10 @@
       <c r="D107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7121,7 +7445,10 @@
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7205,9 +7532,12 @@
         </is>
       </c>
       <c r="D109" s="4">
-        <v>1</v>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
+        <v>1</v>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7298,9 +7628,12 @@
         </is>
       </c>
       <c r="D110" s="4">
-        <v>1</v>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E110" s="4">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7328,7 +7661,10 @@
       <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="4">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7427,9 +7763,12 @@
         </is>
       </c>
       <c r="D112" s="4">
-        <v>1</v>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7455,9 +7794,12 @@
         </is>
       </c>
       <c r="D113" s="4">
-        <v>1</v>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7558,7 +7900,10 @@
       <c r="D114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="4">
+        <v>1</v>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7664,9 +8009,12 @@
         </is>
       </c>
       <c r="D115" s="4">
-        <v>1</v>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7772,9 +8120,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>5</v>
+      </c>
+      <c r="E116" s="4">
         <v>2</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7880,9 +8231,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>5</v>
+      </c>
+      <c r="E117" s="4">
         <v>3</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7988,9 +8342,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>5</v>
+      </c>
+      <c r="E118" s="4">
         <v>4</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8096,9 +8453,12 @@
         </is>
       </c>
       <c r="D119" s="4">
-        <v>1</v>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8206,7 +8566,10 @@
       <c r="D120" s="4">
         <v>2</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="4">
+        <v>2</v>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8314,7 +8677,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8437,7 +8803,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8493,7 +8862,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8549,7 +8921,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8605,7 +8980,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8661,7 +9039,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8715,9 +9096,12 @@
         </is>
       </c>
       <c r="D127" s="4">
-        <v>1</v>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8773,7 +9157,10 @@
       <c r="D128" s="4">
         <v>2</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="4">
+        <v>2</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8827,9 +9214,12 @@
         </is>
       </c>
       <c r="D129" s="4">
-        <v>1</v>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8899,9 +9289,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>3</v>
+      </c>
+      <c r="E130" s="4">
         <v>2</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8973,7 +9366,10 @@
       <c r="D131" s="4">
         <v>3</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>3</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9045,7 +9441,10 @@
       <c r="D132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9106,9 +9505,12 @@
         </is>
       </c>
       <c r="D133" s="4">
-        <v>1</v>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E133" s="4">
+        <v>1</v>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9179,7 +9581,10 @@
       <c r="D134" s="4">
         <v>2</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="4">
+        <v>2</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9263,9 +9668,12 @@
         </is>
       </c>
       <c r="D135" s="4">
-        <v>1</v>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E135" s="4">
+        <v>1</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9328,7 +9736,10 @@
       <c r="D136" s="4">
         <v>2</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4">
+        <v>2</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9389,9 +9800,12 @@
         </is>
       </c>
       <c r="D137" s="4">
-        <v>1</v>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="E137" s="4">
+        <v>1</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9490,9 +9904,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>47</v>
+      </c>
+      <c r="E138" s="4">
         <v>2</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9591,9 +10008,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>47</v>
+      </c>
+      <c r="E139" s="4">
         <v>3</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9692,9 +10112,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>47</v>
+      </c>
+      <c r="E140" s="4">
         <v>4</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9793,9 +10216,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>47</v>
+      </c>
+      <c r="E141" s="4">
         <v>5</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9894,9 +10320,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>47</v>
+      </c>
+      <c r="E142" s="4">
         <v>6</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9995,9 +10424,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>47</v>
+      </c>
+      <c r="E143" s="4">
         <v>7</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10103,9 +10535,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>47</v>
+      </c>
+      <c r="E144" s="4">
         <v>8</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10204,9 +10639,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>47</v>
+      </c>
+      <c r="E145" s="4">
         <v>9</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10297,9 +10735,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>47</v>
+      </c>
+      <c r="E146" s="4">
         <v>10</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10398,9 +10839,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>47</v>
+      </c>
+      <c r="E147" s="4">
         <v>11</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10514,9 +10958,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>47</v>
+      </c>
+      <c r="E148" s="4">
         <v>12</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10607,9 +11054,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>47</v>
+      </c>
+      <c r="E149" s="4">
         <v>13</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10708,9 +11158,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>47</v>
+      </c>
+      <c r="E150" s="4">
         <v>14</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10854,9 +11307,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>47</v>
+      </c>
+      <c r="E151" s="4">
         <v>15</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10962,9 +11418,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>47</v>
+      </c>
+      <c r="E152" s="4">
         <v>16</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11055,9 +11514,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>47</v>
+      </c>
+      <c r="E153" s="4">
         <v>17</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11148,9 +11610,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>47</v>
+      </c>
+      <c r="E154" s="4">
         <v>18</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11241,9 +11706,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>47</v>
+      </c>
+      <c r="E155" s="4">
         <v>19</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11387,9 +11855,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>47</v>
+      </c>
+      <c r="E156" s="4">
         <v>20</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11490,7 +11961,10 @@
       <c r="D157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="4">
+        <v>1</v>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11562,7 +12036,10 @@
       <c r="D158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="4">
+        <v>1</v>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11623,9 +12100,12 @@
         </is>
       </c>
       <c r="D159" s="4">
-        <v>1</v>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11686,9 +12166,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>9</v>
+      </c>
+      <c r="E160" s="4">
         <v>2</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11749,9 +12232,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>9</v>
+      </c>
+      <c r="E161" s="4">
         <v>3</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11812,9 +12298,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>9</v>
+      </c>
+      <c r="E162" s="4">
         <v>4</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11875,9 +12364,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>9</v>
+      </c>
+      <c r="E163" s="4">
         <v>5</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11938,9 +12430,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>9</v>
+      </c>
+      <c r="E164" s="4">
         <v>6</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12001,9 +12496,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>9</v>
+      </c>
+      <c r="E165" s="4">
         <v>7</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12064,9 +12562,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>9</v>
+      </c>
+      <c r="E166" s="4">
         <v>8</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12127,9 +12628,12 @@
         </is>
       </c>
       <c r="D167" s="4">
-        <v>1</v>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
+        <v>41</v>
+      </c>
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12220,9 +12724,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>41</v>
+      </c>
+      <c r="E168" s="4">
         <v>2</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12313,9 +12820,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>41</v>
+      </c>
+      <c r="E169" s="4">
         <v>3</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12399,9 +12909,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>41</v>
+      </c>
+      <c r="E170" s="4">
         <v>4</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12485,9 +12998,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>41</v>
+      </c>
+      <c r="E171" s="4">
         <v>5</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12578,9 +13094,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>41</v>
+      </c>
+      <c r="E172" s="4">
         <v>6</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12664,9 +13183,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>41</v>
+      </c>
+      <c r="E173" s="4">
         <v>7</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12750,9 +13272,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>41</v>
+      </c>
+      <c r="E174" s="4">
         <v>8</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12836,9 +13361,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>41</v>
+      </c>
+      <c r="E175" s="4">
         <v>9</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12937,9 +13465,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>41</v>
+      </c>
+      <c r="E176" s="4">
         <v>10</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13023,9 +13554,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>41</v>
+      </c>
+      <c r="E177" s="4">
         <v>11</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13124,9 +13658,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>41</v>
+      </c>
+      <c r="E178" s="4">
         <v>12</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13210,9 +13747,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>41</v>
+      </c>
+      <c r="E179" s="4">
         <v>13</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13303,9 +13843,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>41</v>
+      </c>
+      <c r="E180" s="4">
         <v>14</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13389,9 +13932,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>41</v>
+      </c>
+      <c r="E181" s="4">
         <v>15</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13482,9 +14028,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>41</v>
+      </c>
+      <c r="E182" s="4">
         <v>16</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13568,9 +14117,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>41</v>
+      </c>
+      <c r="E183" s="4">
         <v>17</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13654,9 +14206,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>41</v>
+      </c>
+      <c r="E184" s="4">
         <v>18</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13740,9 +14295,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>41</v>
+      </c>
+      <c r="E185" s="4">
         <v>19</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13826,9 +14384,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>41</v>
+      </c>
+      <c r="E186" s="4">
         <v>20</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13919,9 +14480,12 @@
         </is>
       </c>
       <c r="D187" s="4">
-        <v>1</v>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E187" s="4">
+        <v>1</v>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13982,9 +14546,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>5</v>
+      </c>
+      <c r="E188" s="4">
         <v>2</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14045,9 +14612,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>5</v>
+      </c>
+      <c r="E189" s="4">
         <v>3</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14108,9 +14678,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>5</v>
+      </c>
+      <c r="E190" s="4">
         <v>4</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14173,7 +14746,10 @@
       <c r="D191" s="4">
         <v>5</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>5</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14236,7 +14812,10 @@
       <c r="D192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14305,9 +14884,12 @@
         </is>
       </c>
       <c r="D193" s="4">
-        <v>1</v>
-      </c>
-      <c r="E193" s="6" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14383,9 +14965,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>9</v>
+      </c>
+      <c r="E194" s="4">
         <v>2</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14461,9 +15046,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>9</v>
+      </c>
+      <c r="E195" s="4">
         <v>3</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14539,9 +15127,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>9</v>
+      </c>
+      <c r="E196" s="4">
         <v>4</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14617,9 +15208,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>9</v>
+      </c>
+      <c r="E197" s="4">
         <v>5</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14695,9 +15289,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>9</v>
+      </c>
+      <c r="E198" s="4">
         <v>6</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14773,9 +15370,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>9</v>
+      </c>
+      <c r="E199" s="4">
         <v>7</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14851,9 +15451,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>9</v>
+      </c>
+      <c r="E200" s="4">
         <v>8</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14931,7 +15534,10 @@
       <c r="D201" s="4">
         <v>9</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="4">
+        <v>9</v>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15007,9 +15613,12 @@
         </is>
       </c>
       <c r="D202" s="4">
-        <v>1</v>
-      </c>
-      <c r="E202" s="6" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="E202" s="4">
+        <v>1</v>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15100,9 +15709,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>8</v>
+      </c>
+      <c r="E203" s="4">
         <v>2</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15186,9 +15798,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>8</v>
+      </c>
+      <c r="E204" s="4">
         <v>3</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15272,9 +15887,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>8</v>
+      </c>
+      <c r="E205" s="4">
         <v>4</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15358,9 +15976,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>8</v>
+      </c>
+      <c r="E206" s="4">
         <v>5</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15444,9 +16065,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>8</v>
+      </c>
+      <c r="E207" s="4">
         <v>6</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15530,9 +16154,12 @@
         </is>
       </c>
       <c r="D208" s="4">
+        <v>8</v>
+      </c>
+      <c r="E208" s="4">
         <v>7</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15618,7 +16245,10 @@
       <c r="D209" s="4">
         <v>8</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="4">
+        <v>8</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15702,9 +16332,12 @@
         </is>
       </c>
       <c r="D210" s="4">
-        <v>1</v>
-      </c>
-      <c r="E210" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E210" s="4">
+        <v>1</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15767,7 +16400,10 @@
       <c r="D211" s="4">
         <v>2</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E211" s="4">
+        <v>2</v>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15830,7 +16466,10 @@
       <c r="D212" s="4">
         <v>1</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="4">
+        <v>1</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15902,7 +16541,10 @@
       <c r="D213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="4">
+        <v>1</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15965,7 +16607,10 @@
       <c r="D214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="4">
+        <v>1</v>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16026,9 +16671,12 @@
         </is>
       </c>
       <c r="D215" s="4">
-        <v>1</v>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E215" s="4">
+        <v>1</v>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16134,9 +16782,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>3</v>
+      </c>
+      <c r="E216" s="4">
         <v>2</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16244,7 +16895,10 @@
       <c r="D217" s="4">
         <v>3</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="4">
+        <v>3</v>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16390,7 +17044,10 @@
       <c r="D218" s="4">
         <v>1</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="4">
+        <v>1</v>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16453,7 +17110,10 @@
       <c r="D219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="4">
+        <v>1</v>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16537,9 +17197,12 @@
         </is>
       </c>
       <c r="D220" s="4">
-        <v>1</v>
-      </c>
-      <c r="E220" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E220" s="4">
+        <v>1</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16602,7 +17265,10 @@
       <c r="D221" s="4">
         <v>2</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="4">
+        <v>2</v>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16663,9 +17329,12 @@
         </is>
       </c>
       <c r="D222" s="4">
-        <v>1</v>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E222" s="4">
+        <v>1</v>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16726,9 +17395,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>4</v>
+      </c>
+      <c r="E223" s="4">
         <v>2</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16789,9 +17461,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>4</v>
+      </c>
+      <c r="E224" s="4">
         <v>3</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16854,7 +17529,10 @@
       <c r="D225" s="4">
         <v>1</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="4">
+        <v>1</v>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16923,9 +17601,12 @@
         </is>
       </c>
       <c r="D226" s="4">
-        <v>1</v>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E226" s="4">
+        <v>1</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16995,9 +17676,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>3</v>
+      </c>
+      <c r="E227" s="4">
         <v>2</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17069,7 +17753,10 @@
       <c r="D228" s="4">
         <v>3</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="4">
+        <v>3</v>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17141,7 +17828,10 @@
       <c r="D229" s="4">
         <v>1</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="4">
+        <v>1</v>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17213,7 +17903,10 @@
       <c r="D230" s="4">
         <v>1</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="4">
+        <v>1</v>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17283,9 +17976,12 @@
         </is>
       </c>
       <c r="D231" s="4">
-        <v>1</v>
-      </c>
-      <c r="E231" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E231" s="4">
+        <v>1</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17355,9 +18051,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>4</v>
+      </c>
+      <c r="E232" s="4">
         <v>2</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17427,9 +18126,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>4</v>
+      </c>
+      <c r="E233" s="4">
         <v>3</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17501,7 +18203,10 @@
       <c r="D234" s="4">
         <v>4</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="E234" s="4">
+        <v>4</v>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17571,9 +18276,12 @@
         </is>
       </c>
       <c r="D235" s="4">
-        <v>1</v>
-      </c>
-      <c r="E235" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E235" s="4">
+        <v>1</v>
+      </c>
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17645,7 +18353,10 @@
       <c r="D236" s="4">
         <v>2</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="4">
+        <v>2</v>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17715,9 +18426,12 @@
         </is>
       </c>
       <c r="D237" s="4">
-        <v>1</v>
-      </c>
-      <c r="E237" s="6" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="E237" s="4">
+        <v>1</v>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17787,9 +18501,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>7</v>
+      </c>
+      <c r="E238" s="4">
         <v>2</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17859,9 +18576,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>7</v>
+      </c>
+      <c r="E239" s="4">
         <v>3</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17931,9 +18651,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>7</v>
+      </c>
+      <c r="E240" s="4">
         <v>4</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18003,9 +18726,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>7</v>
+      </c>
+      <c r="E241" s="4">
         <v>5</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18075,9 +18801,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>7</v>
+      </c>
+      <c r="E242" s="4">
         <v>6</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18149,7 +18878,10 @@
       <c r="D243" s="4">
         <v>7</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="4">
+        <v>7</v>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18219,9 +18951,12 @@
         </is>
       </c>
       <c r="D244" s="4">
-        <v>1</v>
-      </c>
-      <c r="E244" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E244" s="4">
+        <v>1</v>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18291,9 +19026,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>5</v>
+      </c>
+      <c r="E245" s="4">
         <v>2</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18363,9 +19101,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>5</v>
+      </c>
+      <c r="E246" s="4">
         <v>3</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18435,9 +19176,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>5</v>
+      </c>
+      <c r="E247" s="4">
         <v>4</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18509,7 +19253,10 @@
       <c r="D248" s="4">
         <v>5</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="4">
+        <v>5</v>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18579,9 +19326,12 @@
         </is>
       </c>
       <c r="D249" s="4">
-        <v>1</v>
-      </c>
-      <c r="E249" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E249" s="4">
+        <v>1</v>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18653,7 +19403,10 @@
       <c r="D250" s="4">
         <v>2</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="4">
+        <v>2</v>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18725,7 +19478,10 @@
       <c r="D251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="4">
+        <v>1</v>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18779,115 +19535,151 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="144">
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="A73:A74"/>
     <mergeCell ref="B73:B74"/>
     <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
     <mergeCell ref="A78:A79"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
     <mergeCell ref="A86:A87"/>
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
     <mergeCell ref="A89:A90"/>
     <mergeCell ref="B89:B90"/>
     <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="B92:B93"/>
     <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="A100:A101"/>
     <mergeCell ref="B100:B101"/>
     <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
     <mergeCell ref="A102:A104"/>
     <mergeCell ref="B102:B104"/>
     <mergeCell ref="C102:C104"/>
+    <mergeCell ref="D102:D104"/>
     <mergeCell ref="A115:A118"/>
     <mergeCell ref="B115:B118"/>
     <mergeCell ref="C115:C118"/>
+    <mergeCell ref="D115:D118"/>
     <mergeCell ref="A119:A120"/>
     <mergeCell ref="B119:B120"/>
     <mergeCell ref="C119:C120"/>
+    <mergeCell ref="D119:D120"/>
     <mergeCell ref="A127:A128"/>
     <mergeCell ref="B127:B128"/>
     <mergeCell ref="C127:C128"/>
+    <mergeCell ref="D127:D128"/>
     <mergeCell ref="A129:A131"/>
     <mergeCell ref="B129:B131"/>
     <mergeCell ref="C129:C131"/>
+    <mergeCell ref="D129:D131"/>
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="B133:B134"/>
     <mergeCell ref="C133:C134"/>
+    <mergeCell ref="D133:D134"/>
     <mergeCell ref="A135:A136"/>
     <mergeCell ref="B135:B136"/>
     <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:D136"/>
     <mergeCell ref="A137:A156"/>
     <mergeCell ref="B137:B156"/>
     <mergeCell ref="C137:C156"/>
+    <mergeCell ref="D137:D156"/>
     <mergeCell ref="A159:A166"/>
     <mergeCell ref="B159:B166"/>
     <mergeCell ref="C159:C166"/>
+    <mergeCell ref="D159:D166"/>
     <mergeCell ref="A167:A186"/>
     <mergeCell ref="B167:B186"/>
     <mergeCell ref="C167:C186"/>
+    <mergeCell ref="D167:D186"/>
     <mergeCell ref="A187:A191"/>
     <mergeCell ref="B187:B191"/>
     <mergeCell ref="C187:C191"/>
+    <mergeCell ref="D187:D191"/>
     <mergeCell ref="A193:A201"/>
     <mergeCell ref="B193:B201"/>
     <mergeCell ref="C193:C201"/>
+    <mergeCell ref="D193:D201"/>
     <mergeCell ref="A202:A209"/>
     <mergeCell ref="B202:B209"/>
     <mergeCell ref="C202:C209"/>
+    <mergeCell ref="D202:D209"/>
     <mergeCell ref="A210:A211"/>
     <mergeCell ref="B210:B211"/>
     <mergeCell ref="C210:C211"/>
+    <mergeCell ref="D210:D211"/>
     <mergeCell ref="A215:A217"/>
     <mergeCell ref="B215:B217"/>
     <mergeCell ref="C215:C217"/>
+    <mergeCell ref="D215:D217"/>
     <mergeCell ref="A220:A221"/>
     <mergeCell ref="B220:B221"/>
     <mergeCell ref="C220:C221"/>
+    <mergeCell ref="D220:D221"/>
     <mergeCell ref="A222:A224"/>
     <mergeCell ref="B222:B224"/>
     <mergeCell ref="C222:C224"/>
+    <mergeCell ref="D222:D224"/>
     <mergeCell ref="A226:A228"/>
     <mergeCell ref="B226:B228"/>
     <mergeCell ref="C226:C228"/>
+    <mergeCell ref="D226:D228"/>
     <mergeCell ref="A231:A234"/>
     <mergeCell ref="B231:B234"/>
     <mergeCell ref="C231:C234"/>
+    <mergeCell ref="D231:D234"/>
     <mergeCell ref="A235:A236"/>
     <mergeCell ref="B235:B236"/>
     <mergeCell ref="C235:C236"/>
+    <mergeCell ref="D235:D236"/>
     <mergeCell ref="A237:A243"/>
     <mergeCell ref="B237:B243"/>
     <mergeCell ref="C237:C243"/>
+    <mergeCell ref="D237:D243"/>
     <mergeCell ref="A244:A248"/>
     <mergeCell ref="B244:B248"/>
     <mergeCell ref="C244:C248"/>
+    <mergeCell ref="D244:D248"/>
     <mergeCell ref="A249:A250"/>
     <mergeCell ref="B249:B250"/>
     <mergeCell ref="C249:C250"/>
+    <mergeCell ref="D249:D250"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
